--- a/hall/resources/sample/SeasonRanking.xlsx
+++ b/hall/resources/sample/SeasonRanking.xlsx
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="50">
   <si>
     <t>序列ID</t>
   </si>
@@ -267,6 +267,42 @@
   </si>
   <si>
     <t>151_200</t>
+  </si>
+  <si>
+    <t>1960000_80000</t>
+  </si>
+  <si>
+    <t>1960000_60000</t>
+  </si>
+  <si>
+    <t>1960000_45000</t>
+  </si>
+  <si>
+    <t>1960000_40000</t>
+  </si>
+  <si>
+    <t>1960000_35000</t>
+  </si>
+  <si>
+    <t>1960000_30000</t>
+  </si>
+  <si>
+    <t>1960000_25000</t>
+  </si>
+  <si>
+    <t>1960000_15000</t>
+  </si>
+  <si>
+    <t>1960000_8000</t>
+  </si>
+  <si>
+    <t>1960000_7000</t>
+  </si>
+  <si>
+    <t>1960000_6000</t>
+  </si>
+  <si>
+    <t>1960000_5000</t>
   </si>
 </sst>
 </file>
@@ -2324,7 +2360,7 @@
         <v>18</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F43" s="9"/>
       <c r="G43" s="11"/>
@@ -2343,7 +2379,7 @@
         <v>18</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F44" s="9"/>
       <c r="G44" s="11"/>
@@ -2362,7 +2398,7 @@
         <v>18</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="F45" s="9"/>
       <c r="G45" s="11"/>
@@ -2381,7 +2417,7 @@
         <v>18</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="F46" s="9"/>
       <c r="G46" s="11"/>
@@ -2400,7 +2436,7 @@
         <v>18</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F47" s="9"/>
       <c r="G47" s="11"/>
@@ -2419,7 +2455,7 @@
         <v>18</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="F48" s="9"/>
       <c r="G48" s="11"/>
@@ -2438,7 +2474,7 @@
         <v>18</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="F49" s="9"/>
       <c r="G49" s="11"/>
@@ -2457,7 +2493,7 @@
         <v>18</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="F50" s="9"/>
       <c r="G50" s="11"/>
@@ -2476,7 +2512,7 @@
         <v>18</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="F51" s="9"/>
       <c r="G51" s="11"/>
@@ -2495,7 +2531,7 @@
         <v>18</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="F52" s="9"/>
       <c r="G52" s="11"/>
@@ -2514,7 +2550,7 @@
         <v>18</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F53" s="9"/>
       <c r="G53" s="11"/>
@@ -2533,7 +2569,7 @@
         <v>18</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="F54" s="9"/>
       <c r="G54" s="11"/>
@@ -2552,7 +2588,7 @@
         <v>18</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F55" s="9"/>
       <c r="G55" s="11"/>
@@ -2571,7 +2607,7 @@
         <v>18</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="F56" s="9"/>
       <c r="G56" s="11"/>
@@ -2590,7 +2626,7 @@
         <v>18</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F57" s="9"/>
       <c r="G57" s="11"/>
@@ -2609,7 +2645,7 @@
         <v>18</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F58" s="9"/>
       <c r="G58" s="11"/>
@@ -2628,7 +2664,7 @@
         <v>18</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="F59" s="9"/>
       <c r="G59" s="11"/>
@@ -2647,7 +2683,7 @@
         <v>18</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F60" s="9"/>
       <c r="G60" s="11"/>
@@ -2666,7 +2702,7 @@
         <v>18</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="F61" s="9"/>
       <c r="G61" s="11"/>

--- a/hall/resources/sample/SeasonRanking.xlsx
+++ b/hall/resources/sample/SeasonRanking.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
@@ -153,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="57">
   <si>
     <t>序列ID</t>
   </si>
@@ -269,40 +274,61 @@
     <t>151_200</t>
   </si>
   <si>
-    <t>1960000_80000</t>
-  </si>
-  <si>
-    <t>1960000_60000</t>
-  </si>
-  <si>
-    <t>1960000_45000</t>
-  </si>
-  <si>
-    <t>1960000_40000</t>
-  </si>
-  <si>
-    <t>1960000_35000</t>
-  </si>
-  <si>
-    <t>1960000_30000</t>
-  </si>
-  <si>
-    <t>1960000_25000</t>
-  </si>
-  <si>
-    <t>1960000_15000</t>
-  </si>
-  <si>
-    <t>1960000_8000</t>
-  </si>
-  <si>
-    <t>1960000_7000</t>
-  </si>
-  <si>
-    <t>1960000_6000</t>
-  </si>
-  <si>
-    <t>1960000_5000</t>
+    <t>1960000_200000|1024013_100|1024014_100</t>
+  </si>
+  <si>
+    <t>1960000_100000|1024013_90|1024014_90</t>
+  </si>
+  <si>
+    <t>1960000_80000|1024013_80|1024014_80</t>
+  </si>
+  <si>
+    <t>1960000_60000|1024013_70|1024014_70</t>
+  </si>
+  <si>
+    <t>1960000_50000|1024013_60|1024014_60</t>
+  </si>
+  <si>
+    <t>1960000_45000|1024013_50|1024014_50</t>
+  </si>
+  <si>
+    <t>1960000_40000|1024013_40|1024014_40</t>
+  </si>
+  <si>
+    <t>1960000_35000|1024013_30|1024014_30</t>
+  </si>
+  <si>
+    <t>1960000_30000|1024013_20|1024014_20</t>
+  </si>
+  <si>
+    <t>1960000_25000|1024013_15|1024014_15</t>
+  </si>
+  <si>
+    <t>1960000_20000|1024013_10|1024014_10</t>
+  </si>
+  <si>
+    <t>1960000_15000|1024013_5|1024007_50</t>
+  </si>
+  <si>
+    <t>1960000_10000|1024013_5|1024007_45</t>
+  </si>
+  <si>
+    <t>1960000_8000|1024013_5|1024007_40</t>
+  </si>
+  <si>
+    <t>1960000_8000|1024013_5|1024007_35</t>
+  </si>
+  <si>
+    <t>1960000_8000|1024013_5|1024007_30</t>
+  </si>
+  <si>
+    <t>1960000_7000|1024013_5|1024007_20</t>
+  </si>
+  <si>
+    <t>1960000_6000|1024013_5|1024007_10</t>
+  </si>
+  <si>
+    <t>1960000_5000|1024013_5|1024007_5</t>
   </si>
 </sst>
 </file>
@@ -1541,7 +1567,7 @@
     <col min="2" max="2" width="9.125" customWidth="1"/>
     <col min="3" max="3" width="10.875" customWidth="1"/>
     <col min="4" max="4" width="11.75" customWidth="1"/>
-    <col min="5" max="5" width="22.25" customWidth="1"/>
+    <col min="5" max="5" width="30.75" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
     <col min="7" max="7" width="16.5" customWidth="1"/>
   </cols>
@@ -2360,7 +2386,7 @@
         <v>18</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="F43" s="9"/>
       <c r="G43" s="11"/>
@@ -2379,7 +2405,7 @@
         <v>18</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F44" s="9"/>
       <c r="G44" s="11"/>
@@ -2398,7 +2424,7 @@
         <v>18</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F45" s="9"/>
       <c r="G45" s="11"/>
@@ -2417,7 +2443,7 @@
         <v>18</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F46" s="9"/>
       <c r="G46" s="11"/>
@@ -2436,7 +2462,7 @@
         <v>18</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F47" s="9"/>
       <c r="G47" s="11"/>
@@ -2455,7 +2481,7 @@
         <v>18</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F48" s="9"/>
       <c r="G48" s="11"/>
@@ -2474,7 +2500,7 @@
         <v>18</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F49" s="9"/>
       <c r="G49" s="11"/>
@@ -2493,7 +2519,7 @@
         <v>18</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F50" s="9"/>
       <c r="G50" s="11"/>
@@ -2512,7 +2538,7 @@
         <v>18</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F51" s="9"/>
       <c r="G51" s="11"/>
@@ -2531,7 +2557,7 @@
         <v>18</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F52" s="9"/>
       <c r="G52" s="11"/>
@@ -2550,7 +2576,7 @@
         <v>18</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="F53" s="9"/>
       <c r="G53" s="11"/>
@@ -2569,7 +2595,7 @@
         <v>18</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F54" s="9"/>
       <c r="G54" s="11"/>
@@ -2588,7 +2614,7 @@
         <v>18</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="F55" s="9"/>
       <c r="G55" s="11"/>
@@ -2607,7 +2633,7 @@
         <v>18</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F56" s="9"/>
       <c r="G56" s="11"/>
@@ -2626,7 +2652,7 @@
         <v>18</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F57" s="9"/>
       <c r="G57" s="11"/>
@@ -2645,7 +2671,7 @@
         <v>18</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F58" s="9"/>
       <c r="G58" s="11"/>
@@ -2664,7 +2690,7 @@
         <v>18</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F59" s="9"/>
       <c r="G59" s="11"/>
@@ -2683,7 +2709,7 @@
         <v>18</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F60" s="9"/>
       <c r="G60" s="11"/>
@@ -2702,7 +2728,7 @@
         <v>18</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F61" s="9"/>
       <c r="G61" s="11"/>
